--- a/tests/integration_workspace/review_classification_full/output/FINAL_REPORT.xlsx
+++ b/tests/integration_workspace/review_classification_full/output/FINAL_REPORT.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11 sec</t>
+          <t>10 sec</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,17 @@
           <t>SKU-APPLE</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SVO shampoo apple 1 l</t>
+        </is>
+      </c>
       <c r="D2" t="n">
         <v>35.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-05T18:57:07.023915+00:00</t>
+          <t>2026-08-06T16:38:45.861139+00:00</t>
         </is>
       </c>
     </row>
@@ -911,7 +916,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DATE              : 05.08.2026</t>
+          <t>DATE              : 06.08.2026</t>
         </is>
       </c>
     </row>

--- a/tests/integration_workspace/review_classification_full/output/FINAL_REPORT.xlsx
+++ b/tests/integration_workspace/review_classification_full/output/FINAL_REPORT.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10 sec</t>
+          <t>7 sec</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-06T16:38:45.861139+00:00</t>
+          <t>2026-09-03T09:09:03.099507+00:00</t>
         </is>
       </c>
     </row>
@@ -683,99 +683,122 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>НАИМЕНОВАНИЕ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Тип товара</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Бренд</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Variant</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Объем</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>MATCH_STATUS</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>MATCH_SKU</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>MATCH_MASTER_NAME</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>MATCH_CONFIDENCE</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>MATCH_REASONS</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Отгружено</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Шампунь SVO APPLE 1 л</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>SKU-APPLE</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Шампунь</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>SVO</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>APPLE</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>1 л</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>SKU-APPLE</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>SVO SHAMPUN APPLE 1 л</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>100</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -916,7 +939,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DATE              : 06.08.2026</t>
+          <t>DATE              : 03.09.2026</t>
         </is>
       </c>
     </row>
